--- a/artfynd/A 47498-2023 artfynd.xlsx
+++ b/artfynd/A 47498-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47498-2023 artfynd.xlsx
+++ b/artfynd/A 47498-2023 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>683730</v>
+        <v>68320869</v>
       </c>
       <c r="B2" t="n">
-        <v>96056</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1903</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandnate</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Potamogeton compressus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalvnoret, mellan Kalven och Balsjön, 6,7 km norr om Hällesjö k:a, Jmt</t>
+          <t>Kalven / V /, Grundsjöberget / O /, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561335.5238226588</v>
+        <v>561230</v>
       </c>
       <c r="R2" t="n">
-        <v>6982809.136718413</v>
+        <v>6982447</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +738,24 @@
           <t>Hällesjö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Z-Brä-1378</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-08-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering. Grundsjöberget. Koordinat O1520510, N6983964 (±100m). Kopia till floraväkteriet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,54 +769,49 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i sjö, ganska nära stranden</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Via Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Nateinventering Jämtland 2008</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68320881</v>
+        <v>683730</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>1903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Bandnate</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Potamogeton compressus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,34 +819,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalven / V /, Grundsjöberget / O /, Jmt</t>
+          <t>Kalvnoret, mellan Kalven och Balsjön, 6,7 km norr om Hällesjö k:a, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561229.7960209877</v>
+        <v>561336</v>
       </c>
       <c r="R3" t="n">
-        <v>6982446.804324322</v>
+        <v>6982809</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,34 +854,14 @@
           <t>Hällesjö</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Z-Brä-1378</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>116 skott, varav 12 blommande och 104 vegetativa. De flera små dellokalerna var spridda mellan sjön och vägen ca 25 m från och vägen.</t>
+          <t>2008-08-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,23 +875,23 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Från sumpgranskog närmast sjön till mer fuktig granskog närmare vägen där det också silade ner vatten från en vägtrumma</t>
+          <t>i sjö, ganska nära stranden</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Marsha Thalin, Monica Svensson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Nateinventering Jämtland 2008</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 47498-2023 artfynd.xlsx
+++ b/artfynd/A 47498-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68320869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Nateinventering Jämtland 2008</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/683730</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>